--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="18">
   <si>
     <t>_Id</t>
   </si>
@@ -80,10 +85,7 @@
     <t>5001,5014</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>200,100</t>
+    <t>2000,15</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1044,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:J13"/>
+  <dimension ref="C3:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1056,7 +1058,7 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="1:10">
+    <row r="3" customHeight="1" spans="3:10">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1082,7 +1084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:10">
+    <row r="4" customHeight="1" spans="3:10">
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1108,7 +1110,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:10">
+    <row r="5" customHeight="1" spans="3:10">
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1134,7 +1136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:10">
+    <row r="6" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1160,7 +1162,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:10">
+    <row r="7" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1186,7 +1188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:10">
+    <row r="8" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1212,7 +1214,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:10">
+    <row r="9" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1238,13 +1240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:10">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
+    <row r="10" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1255,28 +1251,22 @@
         <v>1001</v>
       </c>
       <c r="F10" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:10">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>17</v>
-      </c>
+    <row r="11" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1287,28 +1277,22 @@
         <v>1002</v>
       </c>
       <c r="F11" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G11" s="1">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:10">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
+    <row r="12" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1319,28 +1303,22 @@
         <v>1003</v>
       </c>
       <c r="F12" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:10">
-      <c r="A13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
+    <row r="13" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1351,16 +1329,16 @@
         <v>1004</v>
       </c>
       <c r="F13" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G13" s="1">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>13</v>
